--- a/backend/data/financials_by_company/107590.KS.xlsx
+++ b/backend/data/financials_by_company/107590.KS.xlsx
@@ -4609,10 +4609,8 @@
           <t>Yongin-si</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>16864</t>
-        </is>
+      <c r="D2" t="n">
+        <v>16864</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4725,7 +4723,7 @@
         <v>0.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>1084</v>
